--- a/scripts/out_syscohada/balance_sn.xlsx
+++ b/scripts/out_syscohada/balance_sn.xlsx
@@ -16,7 +16,7 @@
     <t>YAHRIA BUSINESS OS — ÉTATS FINANCIERS SYSCOHADA (SYSTÈME NORMAL)</t>
   </si>
   <si>
-    <t>SAHEL AGRO INDUSTRIES SA · NCC 00451287 B · RCCM SN-DKR-2016-B-9876 · SN · Monnaie : XOF</t>
+    <t>SAHEL AGRO INDUSTRIES SA · NINEA 00451287 B · RCCM SN-DKR-2016-B-9876 · SN · Monnaie : XOF</t>
   </si>
   <si>
     <t>BALANCE GÉNÉRALE DES COMPTES — Période : 01/01/2026 — 31/12/2026</t>
